--- a/Stats Sheet/Round Gaps/Game Changer.xlsx
+++ b/Stats Sheet/Round Gaps/Game Changer.xlsx
@@ -193,10 +193,10 @@
     <x:t>Digitale</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LoganHam1313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Sean081799</x:t>
